--- a/shared/planilla_mes/planilla_2026-08.xlsx
+++ b/shared/planilla_mes/planilla_2026-08.xlsx
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M6" s="10" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="M10" s="10" t="n">
         <v>0</v>
@@ -1907,13 +1907,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="M20" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="O20" s="11" t="n">
         <v>0</v>
@@ -2963,13 +2963,13 @@
         <v>0</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="M36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="O36" s="11" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="10" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="M43" s="10" t="n">
         <v>0</v>
@@ -7385,13 +7385,13 @@
         <v>0</v>
       </c>
       <c r="L103" s="10" t="n">
-        <v>-16</v>
+        <v>26</v>
       </c>
       <c r="M103" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N103" s="10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O103" s="11" t="n">
         <v>0</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>14B</t>
+          <t>14 B</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -7916,7 +7916,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N111" s="10" t="n">
         <v>75</v>
@@ -8837,10 +8837,10 @@
         <v>0</v>
       </c>
       <c r="L125" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M125" s="10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N125" s="10" t="n">
         <v>50</v>
@@ -11285,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="N162" s="10" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="O162" s="11" t="n">
         <v>0</v>
@@ -12467,7 +12467,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="10" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="M180" s="10" t="n">
         <v>0</v>
@@ -12800,10 +12800,10 @@
         <v>100</v>
       </c>
       <c r="M185" s="10" t="n">
-        <v>-18</v>
+        <v>18</v>
       </c>
       <c r="N185" s="10" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="O185" s="11" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>75</v>
       </c>
       <c r="M188" s="10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N188" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O188" s="11" t="n">
         <v>0</v>
@@ -13127,7 +13127,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="10" t="n">
-        <v>-30</v>
+        <v>50</v>
       </c>
       <c r="M190" s="10" t="n">
         <v>0</v>
@@ -13919,7 +13919,7 @@
         <v>0</v>
       </c>
       <c r="L202" s="10" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="M202" s="10" t="n">
         <v>0</v>
@@ -14777,7 +14777,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="10" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="M215" s="10" t="n">
         <v>0</v>
@@ -15110,7 +15110,7 @@
         <v>60</v>
       </c>
       <c r="M220" s="10" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="N220" s="10" t="n">
         <v>50</v>
@@ -16484,7 +16484,7 @@
         <v>5</v>
       </c>
       <c r="I241" s="10" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="J241" s="10" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>0</v>
       </c>
       <c r="L241" s="10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M241" s="10" t="n">
         <v>30</v>
@@ -17618,7 +17618,7 @@
         <v>0</v>
       </c>
       <c r="M258" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N258" s="10" t="n">
         <v>0</v>
@@ -20255,7 +20255,7 @@
         <v>0</v>
       </c>
       <c r="L298" s="10" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="M298" s="10" t="n">
         <v>0</v>
@@ -25805,7 +25805,7 @@
         <v>0</v>
       </c>
       <c r="N382" s="10" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="O382" s="11" t="n">
         <v>0</v>
@@ -35268,10 +35268,14 @@
       </c>
       <c r="B526" s="7" t="inlineStr">
         <is>
-          <t>14A</t>
-        </is>
-      </c>
-      <c r="C526" s="8" t="inlineStr"/>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C526" s="8" t="inlineStr">
+        <is>
+          <t>JUAN SAAVEDRA SAAVEDRA</t>
+        </is>
+      </c>
       <c r="D526" s="7" t="inlineStr">
         <is>
           <t>2026-08</t>

--- a/shared/planilla_mes/planilla_2026-08.xlsx
+++ b/shared/planilla_mes/planilla_2026-08.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U564"/>
+  <dimension ref="A1:U568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4352,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N57" s="10" t="n">
         <v>0</v>
@@ -6461,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M89" s="10" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O103" s="11" t="n">
         <v>0</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>14 B</t>
+          <t>14B</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -7589,7 +7589,7 @@
         <v>0</v>
       </c>
       <c r="N106" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O106" s="11" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M116" s="10" t="n">
         <v>0</v>
@@ -8441,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="L119" s="10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M119" s="10" t="n">
         <v>0</v>
@@ -8837,10 +8837,10 @@
         <v>0</v>
       </c>
       <c r="L125" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M125" s="10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N125" s="10" t="n">
         <v>50</v>
@@ -9827,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M140" s="10" t="n">
         <v>0</v>
@@ -11615,7 +11615,7 @@
         <v>0</v>
       </c>
       <c r="N167" s="10" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="O167" s="11" t="n">
         <v>0</v>
@@ -13328,10 +13328,10 @@
         <v>100</v>
       </c>
       <c r="M193" s="10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N193" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O193" s="11" t="n">
         <v>0</v>
@@ -15041,13 +15041,13 @@
         <v>0</v>
       </c>
       <c r="L219" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N219" s="10" t="n">
         <v>25</v>
-      </c>
-      <c r="M219" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N219" s="10" t="n">
-        <v>45</v>
       </c>
       <c r="O219" s="11" t="n">
         <v>0</v>
@@ -17489,7 +17489,7 @@
         <v>20</v>
       </c>
       <c r="N256" s="10" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="O256" s="11" t="n">
         <v>0</v>
@@ -17618,7 +17618,7 @@
         <v>0</v>
       </c>
       <c r="M258" s="10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N258" s="10" t="n">
         <v>0</v>
@@ -19793,7 +19793,7 @@
         <v>0</v>
       </c>
       <c r="L291" s="10" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M291" s="10" t="n">
         <v>0</v>
@@ -20915,13 +20915,13 @@
         <v>0</v>
       </c>
       <c r="L308" s="10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M308" s="10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N308" s="10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O308" s="11" t="n">
         <v>0</v>
@@ -21248,10 +21248,10 @@
         <v>0</v>
       </c>
       <c r="M313" s="10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N313" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O313" s="11" t="n">
         <v>0</v>
@@ -21779,7 +21779,7 @@
         <v>0</v>
       </c>
       <c r="N321" s="10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O321" s="11" t="n">
         <v>0</v>
@@ -21842,7 +21842,7 @@
         <v>0</v>
       </c>
       <c r="M322" s="10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N322" s="10" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
         <v>0</v>
       </c>
       <c r="N325" s="10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="O325" s="11" t="n">
         <v>0</v>
@@ -22307,7 +22307,7 @@
         <v>0</v>
       </c>
       <c r="N329" s="10" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="O329" s="11" t="n">
         <v>0</v>
@@ -22436,7 +22436,7 @@
         <v>0</v>
       </c>
       <c r="M331" s="10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N331" s="10" t="n">
         <v>0</v>
@@ -22505,7 +22505,7 @@
         <v>0</v>
       </c>
       <c r="N332" s="10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O332" s="11" t="n">
         <v>0</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="M335" s="10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N335" s="10" t="n">
         <v>0</v>
@@ -23225,13 +23225,13 @@
         <v>0</v>
       </c>
       <c r="L343" s="10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M343" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N343" s="10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O343" s="11" t="n">
         <v>0</v>
@@ -24812,7 +24812,7 @@
         <v>0</v>
       </c>
       <c r="M367" s="10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N367" s="10" t="n">
         <v>0</v>
@@ -30488,10 +30488,10 @@
         <v>0</v>
       </c>
       <c r="M453" s="10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N453" s="10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O453" s="11" t="n">
         <v>0</v>
@@ -31874,10 +31874,10 @@
         <v>0</v>
       </c>
       <c r="M474" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N474" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O474" s="11" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
         <v>0</v>
       </c>
       <c r="M489" s="10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N489" s="10" t="n">
         <v>0</v>
@@ -35268,12 +35268,12 @@
       </c>
       <c r="B526" s="7" t="inlineStr">
         <is>
-          <t>14B</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C526" s="8" t="inlineStr">
         <is>
-          <t>JUAN SAAVEDRA SAAVEDRA</t>
+          <t>FAUSTINO POMA PALLACA</t>
         </is>
       </c>
       <c r="D526" s="7" t="inlineStr">
@@ -35306,7 +35306,7 @@
         <v>0</v>
       </c>
       <c r="M526" s="10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N526" s="10" t="n">
         <v>75</v>
@@ -35329,17 +35329,17 @@
     <row r="527">
       <c r="A527" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B527" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C527" s="8" t="inlineStr">
         <is>
-          <t>FAUSTINO POMA PALLACA</t>
+          <t>RENEE MEDRANO MALLMA</t>
         </is>
       </c>
       <c r="D527" s="7" t="inlineStr">
@@ -35375,7 +35375,7 @@
         <v>50</v>
       </c>
       <c r="N527" s="10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O527" s="11" t="n">
         <v>0</v>
@@ -35395,7 +35395,7 @@
     <row r="528">
       <c r="A528" s="7" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B528" s="7" t="inlineStr">
@@ -35405,7 +35405,7 @@
       </c>
       <c r="C528" s="8" t="inlineStr">
         <is>
-          <t>RENEE MEDRANO MALLMA</t>
+          <t>MELQUIADES SULCA HUAMANI</t>
         </is>
       </c>
       <c r="D528" s="7" t="inlineStr">
@@ -35438,10 +35438,10 @@
         <v>0</v>
       </c>
       <c r="M528" s="10" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N528" s="10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O528" s="11" t="n">
         <v>0</v>
@@ -35461,17 +35461,17 @@
     <row r="529">
       <c r="A529" s="7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B529" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C529" s="8" t="inlineStr">
         <is>
-          <t>MELQUIADES SULCA HUAMANI</t>
+          <t>RUTH LURDINA MILLA CRUZ</t>
         </is>
       </c>
       <c r="D529" s="7" t="inlineStr">
@@ -35504,7 +35504,7 @@
         <v>0</v>
       </c>
       <c r="M529" s="10" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N529" s="10" t="n">
         <v>75</v>
@@ -35532,12 +35532,12 @@
       </c>
       <c r="B530" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C530" s="8" t="inlineStr">
         <is>
-          <t>RUTH LURDINA MILLA CRUZ</t>
+          <t>SANTA ANGELICA VALLLADARES DOMINGUEZ</t>
         </is>
       </c>
       <c r="D530" s="7" t="inlineStr">
@@ -35570,10 +35570,10 @@
         <v>0</v>
       </c>
       <c r="M530" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N530" s="10" t="n">
         <v>50</v>
-      </c>
-      <c r="N530" s="10" t="n">
-        <v>75</v>
       </c>
       <c r="O530" s="11" t="n">
         <v>0</v>
@@ -35994,12 +35994,12 @@
       </c>
       <c r="B537" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C537" s="8" t="inlineStr">
         <is>
-          <t>LOLA PARIONA LEYVA</t>
+          <t>FREDY INGA GAMARA</t>
         </is>
       </c>
       <c r="D537" s="7" t="inlineStr">
@@ -36032,10 +36032,10 @@
         <v>0</v>
       </c>
       <c r="M537" s="10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N537" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O537" s="11" t="n">
         <v>0</v>
@@ -36060,12 +36060,12 @@
       </c>
       <c r="B538" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C538" s="8" t="inlineStr">
         <is>
-          <t>YONY JOSE SAMARITANO HERREDIA</t>
+          <t>LOLA PARIONA LEYVA</t>
         </is>
       </c>
       <c r="D538" s="7" t="inlineStr">
@@ -36101,7 +36101,7 @@
         <v>50</v>
       </c>
       <c r="N538" s="10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O538" s="11" t="n">
         <v>0</v>
@@ -36126,12 +36126,12 @@
       </c>
       <c r="B539" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C539" s="8" t="inlineStr">
         <is>
-          <t>JOSE FRANCISCO SAMARITANO HUAPAYA</t>
+          <t>YONY JOSE SAMARITANO HERREDIA</t>
         </is>
       </c>
       <c r="D539" s="7" t="inlineStr">
@@ -36164,7 +36164,7 @@
         <v>0</v>
       </c>
       <c r="M539" s="10" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N539" s="10" t="n">
         <v>50</v>
@@ -36192,12 +36192,12 @@
       </c>
       <c r="B540" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C540" s="8" t="inlineStr">
         <is>
-          <t>TANIA SAMARITANO HERREDIA</t>
+          <t>JOSE FRANCISCO SAMARITANO HUAPAYA</t>
         </is>
       </c>
       <c r="D540" s="7" t="inlineStr">
@@ -36233,7 +36233,7 @@
         <v>30</v>
       </c>
       <c r="N540" s="10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O540" s="11" t="n">
         <v>0</v>
@@ -36253,17 +36253,17 @@
     <row r="541">
       <c r="A541" s="7" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B541" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C541" s="8" t="inlineStr">
         <is>
-          <t>INOCENTA MILLA BOTELLO</t>
+          <t>TANIA SAMARITANO HERREDIA</t>
         </is>
       </c>
       <c r="D541" s="7" t="inlineStr">
@@ -36296,10 +36296,10 @@
         <v>0</v>
       </c>
       <c r="M541" s="10" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N541" s="10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O541" s="11" t="n">
         <v>0</v>
@@ -36319,17 +36319,17 @@
     <row r="542">
       <c r="A542" s="7" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B542" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C542" s="8" t="inlineStr">
         <is>
-          <t>ZENON MARTIN BURGA TORRES</t>
+          <t>INOCENTA MILLA BOTELLO</t>
         </is>
       </c>
       <c r="D542" s="7" t="inlineStr">
@@ -36365,7 +36365,7 @@
         <v>50</v>
       </c>
       <c r="N542" s="10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O542" s="11" t="n">
         <v>0</v>
@@ -36390,12 +36390,12 @@
       </c>
       <c r="B543" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C543" s="8" t="inlineStr">
         <is>
-          <t>NELSON NOE MONTALVO CANO</t>
+          <t>ZENON MARTIN BURGA TORRES</t>
         </is>
       </c>
       <c r="D543" s="7" t="inlineStr">
@@ -36431,7 +36431,7 @@
         <v>50</v>
       </c>
       <c r="N543" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O543" s="11" t="n">
         <v>0</v>
@@ -36451,17 +36451,17 @@
     <row r="544">
       <c r="A544" s="7" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B544" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C544" s="8" t="inlineStr">
         <is>
-          <t>JORGE BARBOZA AMANTE</t>
+          <t>NELSON NOE MONTALVO CANO</t>
         </is>
       </c>
       <c r="D544" s="7" t="inlineStr">
@@ -36517,17 +36517,17 @@
     <row r="545">
       <c r="A545" s="7" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B545" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C545" s="8" t="inlineStr">
         <is>
-          <t>MATILDE MEZA CASTILLEJO</t>
+          <t>JORGE BARBOZA AMANTE</t>
         </is>
       </c>
       <c r="D545" s="7" t="inlineStr">
@@ -36563,7 +36563,7 @@
         <v>50</v>
       </c>
       <c r="N545" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O545" s="11" t="n">
         <v>0</v>
@@ -36588,12 +36588,12 @@
       </c>
       <c r="B546" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C546" s="8" t="inlineStr">
         <is>
-          <t>ROBERTO CARLOS QUISPE ROMAN</t>
+          <t>MATILDE MEZA CASTILLEJO</t>
         </is>
       </c>
       <c r="D546" s="7" t="inlineStr">
@@ -36654,12 +36654,12 @@
       </c>
       <c r="B547" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C547" s="8" t="inlineStr">
         <is>
-          <t>SOSIMO ROJAS TRUJILLO</t>
+          <t>ROBERTO CARLOS QUISPE ROMAN</t>
         </is>
       </c>
       <c r="D547" s="7" t="inlineStr">
@@ -36715,17 +36715,17 @@
     <row r="548">
       <c r="A548" s="7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B548" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C548" s="8" t="inlineStr">
         <is>
-          <t>MARIANELA ELIZABET RIVERA VITATE</t>
+          <t>SOSIMO ROJAS TRUJILLO</t>
         </is>
       </c>
       <c r="D548" s="7" t="inlineStr">
@@ -36758,10 +36758,10 @@
         <v>0</v>
       </c>
       <c r="M548" s="10" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N548" s="10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O548" s="11" t="n">
         <v>0</v>
@@ -36781,15 +36781,19 @@
     <row r="549">
       <c r="A549" s="7" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B549" s="7" t="inlineStr">
         <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C549" s="8" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C549" s="8" t="inlineStr">
+        <is>
+          <t>MAXIMA CARRANZA RODRIGUEZ</t>
+        </is>
+      </c>
       <c r="D549" s="7" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -36817,13 +36821,13 @@
         <v>0</v>
       </c>
       <c r="L549" s="10" t="n">
-        <v>1334</v>
+        <v>0</v>
       </c>
       <c r="M549" s="10" t="n">
         <v>0</v>
       </c>
       <c r="N549" s="10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O549" s="11" t="n">
         <v>0</v>
@@ -36843,17 +36847,17 @@
     <row r="550">
       <c r="A550" s="7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B550" s="7" t="inlineStr">
         <is>
-          <t>11-B</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C550" s="8" t="inlineStr">
         <is>
-          <t>GILVERTO CLEVER SANCHEZ MEZA</t>
+          <t>MARIANELA ELIZABET RIVERA VITATE</t>
         </is>
       </c>
       <c r="D550" s="7" t="inlineStr">
@@ -36886,10 +36890,10 @@
         <v>0</v>
       </c>
       <c r="M550" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N550" s="10" t="n">
         <v>50</v>
-      </c>
-      <c r="N550" s="10" t="n">
-        <v>0</v>
       </c>
       <c r="O550" s="11" t="n">
         <v>0</v>
@@ -36909,17 +36913,17 @@
     <row r="551">
       <c r="A551" s="7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B551" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C551" s="8" t="inlineStr">
         <is>
-          <t>RAUL ROMERO MAYO</t>
+          <t>I.E 20902</t>
         </is>
       </c>
       <c r="D551" s="7" t="inlineStr">
@@ -36952,10 +36956,10 @@
         <v>0</v>
       </c>
       <c r="M551" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="N551" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O551" s="11" t="n">
         <v>0</v>
@@ -36975,17 +36979,17 @@
     <row r="552">
       <c r="A552" s="7" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B552" s="7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11-B</t>
         </is>
       </c>
       <c r="C552" s="8" t="inlineStr">
         <is>
-          <t>YONY CELEDONIO CERVANTES</t>
+          <t>GILVERTO CLEVER SANCHEZ MEZA</t>
         </is>
       </c>
       <c r="D552" s="7" t="inlineStr">
@@ -37018,10 +37022,10 @@
         <v>0</v>
       </c>
       <c r="M552" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="N552" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O552" s="11" t="n">
         <v>0</v>
@@ -37041,17 +37045,17 @@
     <row r="553">
       <c r="A553" s="7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B553" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C553" s="8" t="inlineStr">
         <is>
-          <t>VICTORIA COSME CERNA</t>
+          <t>RAUL ROMERO MAYO</t>
         </is>
       </c>
       <c r="D553" s="7" t="inlineStr">
@@ -37084,7 +37088,7 @@
         <v>0</v>
       </c>
       <c r="M553" s="10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="N553" s="10" t="n">
         <v>75</v>
@@ -37107,17 +37111,17 @@
     <row r="554">
       <c r="A554" s="7" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B554" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C554" s="8" t="inlineStr">
         <is>
-          <t>SAMUEL SAMARITANO ROMERO</t>
+          <t>ALEJANDRO TRUJILLO DIAZ</t>
         </is>
       </c>
       <c r="D554" s="7" t="inlineStr">
@@ -37153,7 +37157,7 @@
         <v>50</v>
       </c>
       <c r="N554" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O554" s="11" t="n">
         <v>0</v>
@@ -37173,17 +37177,17 @@
     <row r="555">
       <c r="A555" s="7" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B555" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C555" s="8" t="inlineStr">
         <is>
-          <t>HERMELINDA CHAVEZ ESPINOZA</t>
+          <t>YONY CELEDONIO CERVANTES</t>
         </is>
       </c>
       <c r="D555" s="7" t="inlineStr">
@@ -37219,7 +37223,7 @@
         <v>20</v>
       </c>
       <c r="N555" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O555" s="11" t="n">
         <v>0</v>
@@ -37239,17 +37243,17 @@
     <row r="556">
       <c r="A556" s="7" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B556" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C556" s="8" t="inlineStr">
         <is>
-          <t>JENY JAIMES TRUJILLO</t>
+          <t>BEATRIZ ROMERO VALLADARES</t>
         </is>
       </c>
       <c r="D556" s="7" t="inlineStr">
@@ -37305,17 +37309,17 @@
     <row r="557">
       <c r="A557" s="7" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B557" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C557" s="8" t="inlineStr">
         <is>
-          <t>RUDI JORDANO ROCA SEBASTIAN</t>
+          <t>VICTORIA COSME CERNA</t>
         </is>
       </c>
       <c r="D557" s="7" t="inlineStr">
@@ -37351,7 +37355,7 @@
         <v>50</v>
       </c>
       <c r="N557" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O557" s="11" t="n">
         <v>0</v>
@@ -37371,17 +37375,17 @@
     <row r="558">
       <c r="A558" s="7" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B558" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C558" s="8" t="inlineStr">
         <is>
-          <t>MARIA PASTOR SALES DE CARRASCO</t>
+          <t>SAMUEL SAMARITANO ROMERO</t>
         </is>
       </c>
       <c r="D558" s="7" t="inlineStr">
@@ -37437,17 +37441,17 @@
     <row r="559">
       <c r="A559" s="7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B559" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C559" s="8" t="inlineStr">
         <is>
-          <t>IVAN FILOMENO CHAVEZ DAMAZO</t>
+          <t>HERMELINDA CHAVEZ ESPINOZA</t>
         </is>
       </c>
       <c r="D559" s="7" t="inlineStr">
@@ -37480,7 +37484,7 @@
         <v>0</v>
       </c>
       <c r="M559" s="10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="N559" s="10" t="n">
         <v>0</v>
@@ -37503,17 +37507,17 @@
     <row r="560">
       <c r="A560" s="7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B560" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C560" s="8" t="inlineStr">
         <is>
-          <t>GABBY ALICIA HEREDIA ESPINOZA</t>
+          <t>JENY JAIMES TRUJILLO</t>
         </is>
       </c>
       <c r="D560" s="7" t="inlineStr">
@@ -37569,17 +37573,17 @@
     <row r="561">
       <c r="A561" s="7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B561" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C561" s="8" t="inlineStr">
         <is>
-          <t>YOLANDA MERCEDES LOZANO MINAYA</t>
+          <t>RUDI JORDANO ROCA SEBASTIAN</t>
         </is>
       </c>
       <c r="D561" s="7" t="inlineStr">
@@ -37612,10 +37616,10 @@
         <v>0</v>
       </c>
       <c r="M561" s="10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N561" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O561" s="11" t="n">
         <v>0</v>
@@ -37635,17 +37639,17 @@
     <row r="562">
       <c r="A562" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B562" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C562" s="8" t="inlineStr">
         <is>
-          <t>ISENIA YESICA CASTILLO BRONCANO</t>
+          <t>MARIA PASTOR SALES DE CARRASCO</t>
         </is>
       </c>
       <c r="D562" s="7" t="inlineStr">
@@ -37701,17 +37705,17 @@
     <row r="563">
       <c r="A563" s="7" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B563" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C563" s="8" t="inlineStr">
         <is>
-          <t>VASQUEZ HHURTADO ORLANDO</t>
+          <t>IVAN FILOMENO CHAVEZ DAMAZO</t>
         </is>
       </c>
       <c r="D563" s="7" t="inlineStr">
@@ -37744,7 +37748,7 @@
         <v>0</v>
       </c>
       <c r="M563" s="10" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N563" s="10" t="n">
         <v>0</v>
@@ -37767,17 +37771,17 @@
     <row r="564">
       <c r="A564" s="7" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B564" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C564" s="8" t="inlineStr">
         <is>
-          <t>ESTHEFANY MAGALY PONTE SANCHEZ</t>
+          <t>GABBY ALICIA HEREDIA ESPINOZA</t>
         </is>
       </c>
       <c r="D564" s="7" t="inlineStr">
@@ -37829,6 +37833,270 @@
       <c r="S564" s="13" t="n"/>
       <c r="T564" s="14" t="n"/>
       <c r="U564" s="15" t="n"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B565" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C565" s="8" t="inlineStr">
+        <is>
+          <t>YOLANDA MERCEDES LOZANO MINAYA</t>
+        </is>
+      </c>
+      <c r="D565" s="7" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E565" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F565" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G565" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N565" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O565" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P565" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q565" s="12">
+        <f>H565+I565+J565+K565+L565+M565+N565+O565+P565</f>
+        <v/>
+      </c>
+      <c r="R565" s="13" t="n"/>
+      <c r="S565" s="13" t="n"/>
+      <c r="T565" s="14" t="n"/>
+      <c r="U565" s="15" t="n"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B566" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C566" s="8" t="inlineStr">
+        <is>
+          <t>ISENIA YESICA CASTILLO BRONCANO</t>
+        </is>
+      </c>
+      <c r="D566" s="7" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E566" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F566" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G566" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H566" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I566" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J566" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K566" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L566" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M566" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N566" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O566" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P566" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q566" s="12">
+        <f>H566+I566+J566+K566+L566+M566+N566+O566+P566</f>
+        <v/>
+      </c>
+      <c r="R566" s="13" t="n"/>
+      <c r="S566" s="13" t="n"/>
+      <c r="T566" s="14" t="n"/>
+      <c r="U566" s="15" t="n"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="7" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B567" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C567" s="8" t="inlineStr">
+        <is>
+          <t>VASQUEZ HHURTADO ORLANDO</t>
+        </is>
+      </c>
+      <c r="D567" s="7" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E567" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F567" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G567" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M567" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O567" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P567" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q567" s="12">
+        <f>H567+I567+J567+K567+L567+M567+N567+O567+P567</f>
+        <v/>
+      </c>
+      <c r="R567" s="13" t="n"/>
+      <c r="S567" s="13" t="n"/>
+      <c r="T567" s="14" t="n"/>
+      <c r="U567" s="15" t="n"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="7" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B568" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C568" s="8" t="inlineStr">
+        <is>
+          <t>ESTHEFANY MAGALY PONTE SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D568" s="7" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E568" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F568" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G568" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H568" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I568" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J568" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K568" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L568" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M568" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N568" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O568" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P568" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q568" s="12">
+        <f>H568+I568+J568+K568+L568+M568+N568+O568+P568</f>
+        <v/>
+      </c>
+      <c r="R568" s="13" t="n"/>
+      <c r="S568" s="13" t="n"/>
+      <c r="T568" s="14" t="n"/>
+      <c r="U568" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
